--- a/public/data/Feriados2026.xlsx
+++ b/public/data/Feriados2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTOSO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20641AB5-BD87-4D7E-A5FA-7479B7A1571E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0907D360-5258-4903-8B58-F4F281859394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F72842CF-8CBE-444C-B90E-9738A728E691}"/>
+    <workbookView xWindow="0" yWindow="380" windowWidth="19200" windowHeight="10080" xr2:uid="{F72842CF-8CBE-444C-B90E-9738A728E691}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <r>
       <t>1 de enero:</t>
@@ -264,6 +264,34 @@
   </si>
   <si>
     <t>Descripcion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">9 de noviembre: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>visita del Papa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">10 de noviembre: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Papa en Cordoba</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -652,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E5F927-3906-44B3-B743-119CA9D0ECEB}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="66.1796875" bestFit="1" customWidth="1"/>
@@ -788,39 +816,55 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>46349</v>
+        <v>46335</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>46363</v>
+        <v>46336</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>46364</v>
+        <v>46349</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
+        <v>46363</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>46364</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>46381</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B20">
-    <sortCondition ref="A2:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B22">
+    <sortCondition ref="A2:A22"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
